--- a/tools/importer/reports/import-article.report.xlsx
+++ b/tools/importer/reports/import-article.report.xlsx
@@ -40,7 +40,7 @@
     <t>en.report.json</t>
   </si>
   <si>
-    <t>["hero-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser","cards-teaser","carousel-slider","carousel-slider","carousel-slider","columns-social"]</t>
+    <t>["hero-teaser","cards-teasers","cards-news","cards-news","cards-news","cards-topic","carousel-slider","carousel-slider","carousel-slider","columns-events","embed-social"]</t>
   </si>
   <si>
     <t>en</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-03T13:10:15.881Z</t>
+    <t>2026-07-06T16:46:17.478Z</t>
   </si>
   <si>
     <t>Homepage | Max-Planck-Gesellschaft</t>
@@ -64,7 +64,7 @@
     <t>26798800/democracy-cannot-be-taken-for-granted.report.json</t>
   </si>
   <si>
-    <t>["article-aside","carousel-slider"]</t>
+    <t>["article-meta","article-aside","cards-news"]</t>
   </si>
   <si>
     <t>26798800/democracy-cannot-be-taken-for-granted</t>
@@ -73,7 +73,7 @@
     <t>article</t>
   </si>
   <si>
-    <t>2026-07-03T15:27:09.890Z</t>
+    <t>2026-07-08T12:31:15.414Z</t>
   </si>
   <si>
     <t>"Democracy cannot be taken for granted" | Max-Planck-Gesellschaft</t>
